--- a/营收报表调试数据集.xlsx
+++ b/营收报表调试数据集.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,36 +569,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A008-M1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HBW</t>
+          <t>FCBGA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A030-M1</t>
+          <t>A009-M1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FCCSP</t>
+          <t>FCBGA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HBW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HBW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HBW</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FCCSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>A031-M1</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>FCCSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FOFCBGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AA</t>
         </is>
       </c>
     </row>
@@ -613,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,7 +850,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A008-M1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -800,7 +872,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A008-M1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -822,7 +894,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A030-M1</t>
+          <t>A009-M1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -844,7 +916,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A030-M1</t>
+          <t>A009-M1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -866,7 +938,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A031-M1</t>
+          <t>A020-M1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -888,20 +960,284 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>出货</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>入料</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>出货</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>入料</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>出货</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>入料</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>出货</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>A031-M1</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>入料</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A031-M1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>出货</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Post</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>入料</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>出货</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>入料</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>出货</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -918,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:AG25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1644,7 +1980,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A008-M1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1653,97 +1989,97 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1753,103 +2089,103 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A030-M1</t>
+          <t>A009-M1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1858,97 +2194,97 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1958,103 +2294,103 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A031-M1</t>
+          <t>A020-M1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2063,97 +2399,97 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -2163,96 +2499,1326 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AG13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Plan in</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Plan out</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>6</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Plan in</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Plan out</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Plan in</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Plan out</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A031-M1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Plan in</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Plan out</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Plan in</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>4</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Plan out</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Plan in</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Plan out</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2267,7 +3833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AF14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2494,397 +4060,904 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="G5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="H5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="J5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="M5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="N5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="O5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="P5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="Q5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="R5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="S5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="U5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="V5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="W5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="X5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="Y5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AA5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AC5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AD5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AE5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A008-M1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="D6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="E6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="G6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="H6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="J6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="K6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="L6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="M6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="N6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="O6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="P6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="Q6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="R6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="S6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="U6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="V6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="W6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="X6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="Y6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="Z6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AB6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AC6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AD6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AE6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AF6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A030-M1</t>
+          <t>A009-M1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="U7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="V7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="W7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="X7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Y7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AA7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AB7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AC7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AD7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>200</v>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" t="n">
+        <v>200</v>
+      </c>
+      <c r="F8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" t="n">
+        <v>200</v>
+      </c>
+      <c r="H8" t="n">
+        <v>200</v>
+      </c>
+      <c r="I8" t="n">
+        <v>200</v>
+      </c>
+      <c r="J8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K8" t="n">
+        <v>200</v>
+      </c>
+      <c r="L8" t="n">
+        <v>200</v>
+      </c>
+      <c r="M8" t="n">
+        <v>200</v>
+      </c>
+      <c r="N8" t="n">
+        <v>200</v>
+      </c>
+      <c r="O8" t="n">
+        <v>200</v>
+      </c>
+      <c r="P8" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>200</v>
+      </c>
+      <c r="R8" t="n">
+        <v>200</v>
+      </c>
+      <c r="S8" t="n">
+        <v>200</v>
+      </c>
+      <c r="T8" t="n">
+        <v>200</v>
+      </c>
+      <c r="U8" t="n">
+        <v>200</v>
+      </c>
+      <c r="V8" t="n">
+        <v>200</v>
+      </c>
+      <c r="W8" t="n">
+        <v>200</v>
+      </c>
+      <c r="X8" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>200</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>150</v>
+      </c>
+      <c r="C9" t="n">
+        <v>150</v>
+      </c>
+      <c r="D9" t="n">
+        <v>150</v>
+      </c>
+      <c r="E9" t="n">
+        <v>150</v>
+      </c>
+      <c r="F9" t="n">
+        <v>150</v>
+      </c>
+      <c r="G9" t="n">
+        <v>150</v>
+      </c>
+      <c r="H9" t="n">
+        <v>150</v>
+      </c>
+      <c r="I9" t="n">
+        <v>150</v>
+      </c>
+      <c r="J9" t="n">
+        <v>150</v>
+      </c>
+      <c r="K9" t="n">
+        <v>150</v>
+      </c>
+      <c r="L9" t="n">
+        <v>150</v>
+      </c>
+      <c r="M9" t="n">
+        <v>150</v>
+      </c>
+      <c r="N9" t="n">
+        <v>150</v>
+      </c>
+      <c r="O9" t="n">
+        <v>150</v>
+      </c>
+      <c r="P9" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>150</v>
+      </c>
+      <c r="R9" t="n">
+        <v>150</v>
+      </c>
+      <c r="S9" t="n">
+        <v>150</v>
+      </c>
+      <c r="T9" t="n">
+        <v>150</v>
+      </c>
+      <c r="U9" t="n">
+        <v>150</v>
+      </c>
+      <c r="V9" t="n">
+        <v>150</v>
+      </c>
+      <c r="W9" t="n">
+        <v>150</v>
+      </c>
+      <c r="X9" t="n">
+        <v>150</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>150</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>60</v>
+      </c>
+      <c r="C10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" t="n">
+        <v>60</v>
+      </c>
+      <c r="G10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" t="n">
+        <v>60</v>
+      </c>
+      <c r="J10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="n">
+        <v>60</v>
+      </c>
+      <c r="L10" t="n">
+        <v>60</v>
+      </c>
+      <c r="M10" t="n">
+        <v>60</v>
+      </c>
+      <c r="N10" t="n">
+        <v>60</v>
+      </c>
+      <c r="O10" t="n">
+        <v>60</v>
+      </c>
+      <c r="P10" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>60</v>
+      </c>
+      <c r="R10" t="n">
+        <v>60</v>
+      </c>
+      <c r="S10" t="n">
+        <v>60</v>
+      </c>
+      <c r="T10" t="n">
+        <v>60</v>
+      </c>
+      <c r="U10" t="n">
+        <v>60</v>
+      </c>
+      <c r="V10" t="n">
+        <v>60</v>
+      </c>
+      <c r="W10" t="n">
+        <v>60</v>
+      </c>
+      <c r="X10" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50</v>
+      </c>
+      <c r="I11" t="n">
+        <v>50</v>
+      </c>
+      <c r="J11" t="n">
+        <v>50</v>
+      </c>
+      <c r="K11" t="n">
+        <v>50</v>
+      </c>
+      <c r="L11" t="n">
+        <v>50</v>
+      </c>
+      <c r="M11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N11" t="n">
+        <v>50</v>
+      </c>
+      <c r="O11" t="n">
+        <v>50</v>
+      </c>
+      <c r="P11" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>50</v>
+      </c>
+      <c r="R11" t="n">
+        <v>50</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="n">
+        <v>50</v>
+      </c>
+      <c r="U11" t="n">
+        <v>50</v>
+      </c>
+      <c r="V11" t="n">
+        <v>50</v>
+      </c>
+      <c r="W11" t="n">
+        <v>50</v>
+      </c>
+      <c r="X11" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>A031-M1</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B12" t="n">
         <v>30</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C12" t="n">
         <v>30</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D12" t="n">
         <v>30</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E12" t="n">
         <v>30</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F12" t="n">
         <v>30</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G12" t="n">
         <v>30</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H12" t="n">
         <v>30</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I12" t="n">
         <v>30</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J12" t="n">
         <v>30</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K12" t="n">
         <v>30</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L12" t="n">
         <v>30</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M12" t="n">
         <v>30</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N12" t="n">
         <v>30</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O12" t="n">
         <v>30</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P12" t="n">
         <v>30</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q12" t="n">
         <v>30</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R12" t="n">
         <v>30</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S12" t="n">
         <v>30</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T12" t="n">
         <v>30</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U12" t="n">
         <v>30</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V12" t="n">
         <v>30</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W12" t="n">
         <v>30</v>
       </c>
-      <c r="X8" t="n">
+      <c r="X12" t="n">
         <v>30</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y12" t="n">
         <v>30</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="Z12" t="n">
         <v>30</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA12" t="n">
         <v>30</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AB12" t="n">
         <v>30</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AC12" t="n">
         <v>30</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AD12" t="n">
         <v>30</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AE12" t="n">
         <v>30</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AF12" t="n">
         <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>25</v>
+      </c>
+      <c r="C14" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G14" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>25</v>
+      </c>
+      <c r="N14" t="n">
+        <v>25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="n">
+        <v>25</v>
+      </c>
+      <c r="U14" t="n">
+        <v>25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>25</v>
+      </c>
+      <c r="X14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2898,7 +4971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2941,7 +5014,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>R001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2969,7 +5042,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>R002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2997,7 +5070,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>R003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3025,7 +5098,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>R004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3038,11 +5111,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A006-M1</t>
+          <t>A005-M1</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3053,7 +5126,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>R005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3066,11 +5139,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A006-M1</t>
+          <t>A005-M1</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3081,7 +5154,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>R006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3090,15 +5163,15 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A005-M1</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46245</v>
+        <v>46259</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3109,7 +5182,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>R007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3118,15 +5191,15 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A030-M1</t>
+          <t>A006-M1</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46246</v>
+        <v>46238</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3137,7 +5210,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>R008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3150,22 +5223,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A006-M1</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>R009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3178,22 +5251,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A006-M1</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46240</v>
+        <v>46254</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L10</t>
+          <t>R010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3202,26 +5275,26 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A006-M1</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46242</v>
+        <v>46262</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L11</t>
+          <t>R011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3230,43 +5303,43 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A030-M1</t>
+          <t>A007-M1</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46237</v>
+        <v>46236</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L12</t>
+          <t>R012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A007-M1</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46239</v>
+        <v>46243</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3277,7 +5350,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L13</t>
+          <t>R013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3286,15 +5359,15 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A007-M1</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46267</v>
+        <v>46250</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3305,7 +5378,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L14</t>
+          <t>R014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3313,23 +5386,1698 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A007-M1</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A009-M1</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>R019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A009-M1</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>R020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A009-M1</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>R022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>R023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>R024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>R026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>R028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>R030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>R031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>46257</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>R032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A031-M1</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>R033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A031-M1</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>R034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>R035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>R036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>R037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>R038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>S042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>S043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>S047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>S048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>A007-M1</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>S049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>A007-M1</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>S050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>A007-M1</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>46256</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>S051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>S052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>S053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A009-M1</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>46243</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A009-M1</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>S055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>10</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>14</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>S057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>9</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>7</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>11</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>S062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>S063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>S064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>S065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>A031-M1</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>S066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>A031-M1</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>S067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>6</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>S068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>S069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>S070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>9</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>7</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>A005-M1</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F74" s="3" t="n">
         <v>46243</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Pre</t>
         </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>46249</v>
       </c>
     </row>
   </sheetData>
@@ -3343,7 +7091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3427,6 +7175,81 @@
         <v>46240</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>plan in</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A007-M1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>scrapped</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>plan out</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>plan out</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>46254</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/营收报表调试数据集.xlsx
+++ b/营收报表调试数据集.xlsx
@@ -24,10 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="m/d"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -58,10 +59,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -726,6 +728,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -748,6 +755,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Post</t>
@@ -770,6 +782,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -792,6 +809,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Post</t>
@@ -814,6 +836,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -836,6 +863,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Post</t>
@@ -858,6 +890,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -880,6 +917,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Post</t>
@@ -902,6 +944,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -924,6 +971,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Post</t>
@@ -946,6 +998,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -968,6 +1025,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Post</t>
@@ -990,6 +1052,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -1012,6 +1079,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Post</t>
@@ -1034,6 +1106,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -1056,6 +1133,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>Post</t>
@@ -1078,6 +1160,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -1100,6 +1187,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Post</t>
@@ -1122,6 +1214,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -1144,6 +1241,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>Post</t>
@@ -1166,6 +1268,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -1188,6 +1295,11 @@
           <t>出货</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>Post</t>
@@ -1210,6 +1322,11 @@
           <t>入料</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Pre</t>
@@ -1230,6 +1347,11 @@
       <c r="B25" t="inlineStr">
         <is>
           <t>出货</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4971,7 +5093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5014,7 +5136,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R001</t>
+          <t>LOT0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5030,8 +5152,13 @@
           <t>A005-M1</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
       <c r="F2" s="3" t="n">
-        <v>46237</v>
+        <v>46237.375</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5042,7 +5169,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R002</t>
+          <t>LOT0002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5051,15 +5178,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>A005-M1</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WIP_ETCH</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="n">
-        <v>46239</v>
+        <v>46238.33333333334</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5070,7 +5202,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R003</t>
+          <t>LOT0003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5079,26 +5211,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>A005-M1</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>WIP_ETCH</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="n">
-        <v>46241</v>
+        <v>46238.70833333334</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R004</t>
+          <t>LOT0004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5107,15 +5244,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>A005-M1</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>WIP_PKG</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="n">
-        <v>46246</v>
+        <v>46239.33333333334</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5126,7 +5268,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>LOT0005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5135,26 +5277,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>A005-M1</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WIP_PKG</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="n">
-        <v>46252</v>
+        <v>46239.70833333334</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>LOT0006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5163,26 +5310,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>A005-M1</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="n">
-        <v>46259</v>
+        <v>46246.75</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R007</t>
+          <t>LOT0007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5191,15 +5343,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A006-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>46238</v>
+        <v>46241.375</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -5210,7 +5367,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>LOT0008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5219,15 +5376,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A006-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>WIP_ETCH</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46245</v>
+        <v>46242.33333333334</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -5238,7 +5400,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R009</t>
+          <t>LOT0009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5247,26 +5409,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A006-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>WIP_ETCH</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46254</v>
+        <v>46242.70833333334</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R010</t>
+          <t>LOT0010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5275,15 +5442,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A006-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WIP_PKG</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46262</v>
+        <v>46243.33333333334</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -5294,7 +5466,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R011</t>
+          <t>LOT0011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5303,26 +5475,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A007-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>WIP_PKG</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46236</v>
+        <v>46243.70833333334</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R012</t>
+          <t>LOT0012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,26 +5508,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A007-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46243</v>
+        <v>46252.75</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R013</t>
+          <t>LOT0013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5359,15 +5541,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A007-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46250</v>
+        <v>46249.375</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -5378,7 +5565,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R014</t>
+          <t>LOT0014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5387,15 +5574,20 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A007-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>WIP_ETCH</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46257</v>
+        <v>46250.33333333334</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -5406,7 +5598,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R015</t>
+          <t>LOT0015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5415,26 +5607,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A008-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>WIP_ETCH</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46240</v>
+        <v>46250.70833333334</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R016</t>
+          <t>LOT0016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5443,15 +5640,20 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A008-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WIP_PKG</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46247</v>
+        <v>46251.33333333334</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -5462,7 +5664,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R017</t>
+          <t>LOT0017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5471,26 +5673,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A008-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>WIP_PKG</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46256</v>
+        <v>46251.70833333334</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R018</t>
+          <t>LOT0018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5499,26 +5706,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A009-M1</t>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46239</v>
+        <v>46262.75</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R019</t>
+          <t>LOT0019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5531,11 +5743,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A009-M1</t>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>46251</v>
+        <v>46238.375</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -5546,7 +5763,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R020</t>
+          <t>LOT0020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5555,15 +5772,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A009-M1</t>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WIP_ASM</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>46261</v>
+        <v>46239.33333333334</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -5574,7 +5796,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R021</t>
+          <t>LOT0021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5583,26 +5805,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>WIP_ASM</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>46245</v>
+        <v>46239.70833333334</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R022</t>
+          <t>LOT0022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5611,26 +5838,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>46253</v>
+        <v>46247.75</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R023</t>
+          <t>LOT0023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5639,15 +5871,20 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>46260</v>
+        <v>46245.375</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -5658,7 +5895,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R024</t>
+          <t>LOT0024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5667,15 +5904,20 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A021-M1</t>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>WIP_ASM</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>46242</v>
+        <v>46246.33333333334</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -5686,7 +5928,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R025</t>
+          <t>LOT0025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5695,26 +5937,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A021-M1</t>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>WIP_ASM</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>46249</v>
+        <v>46246.70833333334</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R026</t>
+          <t>LOT0026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5723,26 +5970,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A021-M1</t>
+          <t>A006-M1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>46258</v>
+        <v>46258.75</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R027</t>
+          <t>LOT0027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5751,15 +6003,20 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A022-M1</t>
+          <t>A007-M1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>46241</v>
+        <v>46236.375</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -5770,7 +6027,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R028</t>
+          <t>LOT0028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5783,22 +6040,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A022-M1</t>
+          <t>A007-M1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>46248</v>
+        <v>46243.75</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R029</t>
+          <t>LOT0029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5807,15 +6069,20 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A022-M1</t>
+          <t>A007-M1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>46255</v>
+        <v>46250.375</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5826,7 +6093,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R030</t>
+          <t>LOT0030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5835,26 +6102,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A030-M1</t>
+          <t>A007-M1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>46246</v>
+        <v>46259.75</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R031</t>
+          <t>LOT0031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5863,15 +6135,20 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A030-M1</t>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>46257</v>
+        <v>46240.375</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -5882,7 +6159,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R032</t>
+          <t>LOT0032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5891,15 +6168,20 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A031-M1</t>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>WIP_SMT</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>46244</v>
+        <v>46241.33333333334</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5910,7 +6192,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R033</t>
+          <t>LOT0033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5919,26 +6201,31 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A031-M1</t>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>WIP_SMT</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>46259</v>
+        <v>46241.70833333334</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R034</t>
+          <t>LOT0034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5947,26 +6234,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A040-M1</t>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>46243</v>
+        <v>46249.75</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R035</t>
+          <t>LOT0035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5975,15 +6267,20 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A040-M1</t>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>46253</v>
+        <v>46256.375</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5994,7 +6291,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R036</t>
+          <t>LOT0036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6003,15 +6300,20 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A040-M1</t>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>WIP_SMT</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>46263</v>
+        <v>46257.33333333334</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6022,7 +6324,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R037</t>
+          <t>LOT0037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6031,26 +6333,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A050-M1</t>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WIP_SMT</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>46245</v>
+        <v>46257.70833333334</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R038</t>
+          <t>LOT0038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6063,22 +6370,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A050-M1</t>
+          <t>A008-M1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>46256</v>
+        <v>46264.75</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S039</t>
+          <t>LOT0039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6087,26 +6399,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A009-M1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>46238</v>
+        <v>46239.375</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S040</t>
+          <t>LOT0040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6115,15 +6432,20 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A009-M1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>46240</v>
+        <v>46248.75</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6134,7 +6456,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S041</t>
+          <t>LOT0041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6143,26 +6465,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>46244</v>
+        <v>46242.375</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S042</t>
+          <t>LOT0042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6171,26 +6498,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>WIP_PLATE</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>46254</v>
+        <v>46243.33333333334</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S043</t>
+          <t>LOT0043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6199,15 +6531,20 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>WIP_PLATE</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>46262</v>
+        <v>46243.70833333334</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -6218,7 +6555,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S044</t>
+          <t>LOT0044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6227,15 +6564,20 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A006-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>46239</v>
+        <v>46247.75</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -6246,7 +6588,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S045</t>
+          <t>LOT0045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6255,26 +6597,31 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A006-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>46246</v>
+        <v>46253.375</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S046</t>
+          <t>LOT0046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6283,26 +6630,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A006-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>WIP_PLATE</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>46255</v>
+        <v>46254.33333333334</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S047</t>
+          <t>LOT0047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6311,15 +6663,20 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A006-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>WIP_PLATE</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>46264</v>
+        <v>46254.70833333334</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6330,7 +6687,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S048</t>
+          <t>LOT0048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6339,15 +6696,20 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>A007-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>46242</v>
+        <v>46258.75</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6358,7 +6720,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S049</t>
+          <t>LOT0049</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6367,26 +6729,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>A007-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>46249</v>
+        <v>46260.375</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S050</t>
+          <t>LOT0050</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6395,26 +6762,31 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A007-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>WIP_PLATE</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>46256</v>
+        <v>46261.33333333334</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S051</t>
+          <t>LOT0051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6423,15 +6795,20 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A008-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>WIP_PLATE</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>46247</v>
+        <v>46261.70833333334</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6442,7 +6819,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S052</t>
+          <t>LOT0052</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6451,15 +6828,20 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A008-M1</t>
+          <t>A020-M1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>46258</v>
+        <v>46264.75</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6470,7 +6852,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S053</t>
+          <t>LOT0053</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6479,26 +6861,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A009-M1</t>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>46243</v>
+        <v>46242.375</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S054</t>
+          <t>LOT0054</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6507,15 +6894,20 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A009-M1</t>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>46252</v>
+        <v>46250.75</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6526,7 +6918,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S055</t>
+          <t>LOT0055</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6535,26 +6927,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>46242</v>
+        <v>46255.375</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S056</t>
+          <t>LOT0056</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6563,15 +6960,20 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A021-M1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>46250</v>
+        <v>46261.75</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6582,7 +6984,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S057</t>
+          <t>LOT0057</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6591,26 +6993,31 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>A020-M1</t>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>46261</v>
+        <v>46244.375</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S058</t>
+          <t>LOT0058</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6619,15 +7026,20 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>A021-M1</t>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>46246</v>
+        <v>46252.75</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -6638,7 +7050,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S059</t>
+          <t>LOT0059</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6647,26 +7059,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>A021-M1</t>
+          <t>A022-M1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>46254</v>
+        <v>46256.375</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S060</t>
+          <t>LOT0060</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6675,15 +7092,20 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>A022-M1</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="F61" s="3" t="n">
-        <v>46249</v>
+        <v>46263.75</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -6694,7 +7116,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S061</t>
+          <t>LOT0061</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6703,26 +7125,31 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>A022-M1</t>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>46260</v>
+        <v>46246.375</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S062</t>
+          <t>LOT0062</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6731,26 +7158,31 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>A030-M1</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>WIP_DIE</t>
+        </is>
+      </c>
       <c r="F63" s="3" t="n">
-        <v>46237</v>
+        <v>46247.33333333334</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S063</t>
+          <t>LOT0063</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6759,15 +7191,20 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>A030-M1</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>WIP_DIE</t>
+        </is>
+      </c>
       <c r="F64" s="3" t="n">
-        <v>46248</v>
+        <v>46247.70833333334</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -6778,7 +7215,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S064</t>
+          <t>LOT0064</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6794,8 +7231,13 @@
           <t>A030-M1</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
       <c r="F65" s="3" t="n">
-        <v>46262</v>
+        <v>46254.75</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -6806,7 +7248,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S065</t>
+          <t>LOT0065</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6819,22 +7261,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>A031-M1</t>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>46247</v>
+        <v>46258.375</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S066</t>
+          <t>LOT0066</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6843,26 +7290,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>A031-M1</t>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>WIP_DIE</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>46261</v>
+        <v>46259.33333333334</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S067</t>
+          <t>LOT0067</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6871,15 +7323,20 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>A040-M1</t>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>WIP_DIE</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>46244</v>
+        <v>46259.70833333334</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -6890,7 +7347,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S068</t>
+          <t>LOT0068</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6903,11 +7360,16 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>A040-M1</t>
+          <t>A030-M1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>46258</v>
+        <v>46262.75</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -6918,7 +7380,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S069</t>
+          <t>LOT0069</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6927,26 +7389,31 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>A050-M1</t>
+          <t>A031-M1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>46250</v>
+        <v>46244.375</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Pre</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S070</t>
+          <t>LOT0070</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6955,15 +7422,20 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>A050-M1</t>
+          <t>A031-M1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>46263</v>
+        <v>46251.75</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -6974,24 +7446,29 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>LOT0071</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A031-M1</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>46239</v>
+        <v>46255.375</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -7002,7 +7479,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>LOT0072</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7011,26 +7488,31 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A031-M1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>46267</v>
+        <v>46261.75</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>LOT0073</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7038,18 +7520,21 @@
           <t>P</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="C74" t="n">
+        <v>9</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>A005-M1</t>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>46243</v>
+        <v>46243.375</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -7060,7 +7545,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>LOT0074</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7069,15 +7554,451 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>46253.75</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>LOT0075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>46258.375</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>LOT0076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>A040-M1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>46263.75</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>LOT0077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>46245.375</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LOT0078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>46250.75</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>LOT0079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>46256.375</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>LOT0080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>5</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>A050-M1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>46263.75</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>LOT0081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>A005-M1</t>
         </is>
       </c>
-      <c r="F75" s="3" t="n">
-        <v>46249</v>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>46239.375</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>LOT0082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>46243.41666666666</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>LOT0083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>46249.375</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>LOT0084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>WIP_ETCH</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>46250.375</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>LOT0085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>5</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OUT_SHIP</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>46251.375</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>LOT0086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>6</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>46236.375</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>LOT0087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>7</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>A005-M1</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>IN_RECV</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>46267.375</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7145,10 +8066,10 @@
           <t>plan in</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>46239</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>46244</v>
       </c>
     </row>
@@ -7171,7 +8092,7 @@
           <t>plan out</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>46240</v>
       </c>
     </row>
@@ -7194,10 +8115,10 @@
           <t>plan in</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>46249</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>46256</v>
       </c>
     </row>
@@ -7220,7 +8141,7 @@
           <t>plan out</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>46242</v>
       </c>
     </row>
@@ -7243,10 +8164,10 @@
           <t>plan out</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>46248</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>46254</v>
       </c>
     </row>
